--- a/data-raw/metadata/knights_landing_recapture_metadata.xlsx
+++ b/data-raw/metadata/knights_landing_recapture_metadata.xlsx
@@ -1,32 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Badhia\Documents\git\jpe-knights-edi\data-raw\metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Inigo\Projects\jpe-knights-edi\data-raw\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E54C7C4-AF55-460A-A1F3-CFEF46786B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC4E9E0-74AF-4242-B6CE-0F8E760646D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3980" yWindow="1740" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attribute" sheetId="1" r:id="rId1"/>
     <sheet name="code_definitions" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataSignature="AMtx7mghxNeI8GvXuJqBqb0qinn6k/u/XQ=="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="70">
   <si>
     <t xml:space="preserve">attribute_name </t>
   </si>
@@ -95,9 +90,6 @@
   </si>
   <si>
     <t>markColor</t>
-  </si>
-  <si>
-    <t>recaptures</t>
   </si>
   <si>
     <t>trapVisitID</t>
@@ -227,12 +219,30 @@
   <si>
     <t>2023-04-27 10:45:43</t>
   </si>
+  <si>
+    <t>trap_start_date</t>
+  </si>
+  <si>
+    <t>trap_end_date</t>
+  </si>
+  <si>
+    <t>Start date and time of a trapping period. Derived from visitTime and visitTime2 fields, adjusted based on the visitType field</t>
+  </si>
+  <si>
+    <t>recapture</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> End date and time of a trapping period. Derived from visitTime and visitTime2 fields, adjusted based on the visitType field</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -257,6 +267,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -296,10 +312,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -339,9 +356,23 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{48B893EA-6A58-420A-B8A0-2937F4FE508A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -628,16 +659,16 @@
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>16</v>
@@ -669,13 +700,13 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
@@ -704,16 +735,16 @@
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -742,16 +773,16 @@
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -780,16 +811,16 @@
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
@@ -818,16 +849,16 @@
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>16</v>
@@ -856,16 +887,16 @@
     </row>
     <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
@@ -894,16 +925,16 @@
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
@@ -932,28 +963,28 @@
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>23</v>
+      <c r="F10" s="14" t="s">
+        <v>43</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="G10" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="14" t="s">
+      <c r="H10" s="14" t="s">
         <v>46</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>47</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="14"/>
@@ -980,28 +1011,28 @@
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="14" t="s">
+      <c r="H11" s="14" t="s">
         <v>50</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>51</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="14"/>
@@ -1028,33 +1059,33 @@
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="D12" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="7"/>
       <c r="J12" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
@@ -1072,16 +1103,16 @@
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>16</v>
@@ -1110,16 +1141,16 @@
     </row>
     <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>16</v>
@@ -1148,16 +1179,16 @@
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -1189,13 +1220,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>16</v>
@@ -1227,13 +1258,13 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>16</v>
@@ -1262,16 +1293,16 @@
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>16</v>
@@ -1303,13 +1334,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>16</v>
@@ -1337,60 +1368,92 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
+      <c r="A20" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="20"/>
+      <c r="L20" s="25">
+        <v>40524.531643518516</v>
+      </c>
+      <c r="M20" s="25">
+        <v>45378.416817129626</v>
+      </c>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="19"/>
+      <c r="U20" s="19"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="19"/>
+      <c r="X20" s="19"/>
+      <c r="Y20" s="19"/>
+      <c r="Z20" s="19"/>
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
+      <c r="A21" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K21" s="24"/>
+      <c r="L21" s="25">
+        <v>40524.531643518516</v>
+      </c>
+      <c r="M21" s="25">
+        <v>45378.416817129626</v>
+      </c>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="19"/>
+      <c r="U21" s="19"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="19"/>
+      <c r="X21" s="19"/>
+      <c r="Y21" s="19"/>
+      <c r="Z21" s="19"/>
     </row>
     <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4"/>

--- a/data-raw/metadata/knights_landing_recapture_metadata.xlsx
+++ b/data-raw/metadata/knights_landing_recapture_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Inigo\Projects\jpe-knights-edi\data-raw\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC4E9E0-74AF-4242-B6CE-0F8E760646D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E5D77A-0F89-420C-A446-12D6597E604C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="72">
   <si>
     <t xml:space="preserve">attribute_name </t>
   </si>
@@ -234,6 +234,12 @@
   <si>
     <t xml:space="preserve"> End date and time of a trapping period. Derived from visitTime and visitTime2 fields, adjusted based on the visitType field</t>
   </si>
+  <si>
+    <t>visitTime2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date and time of day associated with the end of trap visit. Definition varies based on visitType. </t>
+  </si>
 </sst>
 </file>
 
@@ -312,11 +318,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -354,8 +361,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -369,10 +374,23 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{48B893EA-6A58-420A-B8A0-2937F4FE508A}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{5DE3FDDC-740D-43C8-A716-B293F6608B1D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -585,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1001"/>
+  <dimension ref="A1:Z1002"/>
   <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -1101,50 +1119,56 @@
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13" s="30"/>
+      <c r="L13" s="31">
+        <v>40524.531643518516</v>
+      </c>
+      <c r="M13" s="31">
+        <v>45380.416712962964</v>
+      </c>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="26"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="26"/>
+      <c r="U13" s="26"/>
+      <c r="V13" s="26"/>
+      <c r="W13" s="26"/>
+      <c r="X13" s="26"/>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="26"/>
+    </row>
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
-    </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>13</v>
@@ -1161,8 +1185,8 @@
       <c r="I14" s="7"/>
       <c r="J14" s="6"/>
       <c r="K14" s="7"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
@@ -1179,10 +1203,10 @@
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>13</v>
@@ -1217,10 +1241,10 @@
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>13</v>
@@ -1231,34 +1255,34 @@
       <c r="E16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-      <c r="Z16" s="1"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="4"/>
     </row>
     <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>13</v>
@@ -1273,9 +1297,9 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="3"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="10"/>
       <c r="M17" s="3"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -1293,10 +1317,10 @@
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>13</v>
@@ -1331,10 +1355,10 @@
     </row>
     <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>13</v>
@@ -1349,7 +1373,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="3"/>
+      <c r="J19" s="6"/>
       <c r="K19" s="2"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -1368,120 +1392,130 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+    </row>
+    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B21" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C21" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D21" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E21" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="23" t="s">
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="K20" s="20"/>
-      <c r="L20" s="25">
+      <c r="K21" s="18"/>
+      <c r="L21" s="23">
         <v>40524.531643518516</v>
       </c>
-      <c r="M20" s="25">
+      <c r="M21" s="23">
         <v>45378.416817129626</v>
       </c>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
-      <c r="U20" s="19"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19"/>
-      <c r="X20" s="19"/>
-      <c r="Y20" s="19"/>
-      <c r="Z20" s="19"/>
-    </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="22" t="s">
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="17"/>
+      <c r="Z21" s="17"/>
+    </row>
+    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B22" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C22" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D22" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E22" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="23" t="s">
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="K21" s="24"/>
-      <c r="L21" s="25">
+      <c r="K22" s="22"/>
+      <c r="L22" s="23">
         <v>40524.531643518516</v>
       </c>
-      <c r="M21" s="25">
+      <c r="M22" s="23">
         <v>45378.416817129626</v>
       </c>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
-      <c r="U21" s="19"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="19"/>
-      <c r="X21" s="19"/>
-      <c r="Y21" s="19"/>
-      <c r="Z21" s="19"/>
-    </row>
-    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
+      <c r="Z22" s="17"/>
     </row>
     <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4"/>
@@ -1904,7 +1938,7 @@
       <c r="Z37" s="1"/>
     </row>
     <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="17"/>
+      <c r="A38" s="4"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="2"/>
@@ -1932,7 +1966,7 @@
       <c r="Z38" s="1"/>
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="18"/>
+      <c r="A39" s="24"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="2"/>
@@ -1960,7 +1994,7 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="17"/>
+      <c r="A40" s="25"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="2"/>
@@ -1988,7 +2022,7 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="18"/>
+      <c r="A41" s="24"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="2"/>
@@ -2016,7 +2050,7 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="4"/>
+      <c r="A42" s="25"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="2"/>
@@ -2968,7 +3002,7 @@
       <c r="Z75" s="1"/>
     </row>
     <row r="76" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="1"/>
+      <c r="A76" s="4"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="2"/>
@@ -28895,22 +28929,50 @@
       <c r="Y1001" s="1"/>
       <c r="Z1001" s="1"/>
     </row>
+    <row r="1002" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1002" s="1"/>
+      <c r="B1002" s="1"/>
+      <c r="C1002" s="1"/>
+      <c r="D1002" s="2"/>
+      <c r="E1002" s="1"/>
+      <c r="F1002" s="3"/>
+      <c r="G1002" s="3"/>
+      <c r="H1002" s="3"/>
+      <c r="I1002" s="2"/>
+      <c r="J1002" s="3"/>
+      <c r="K1002" s="2"/>
+      <c r="L1002" s="3"/>
+      <c r="M1002" s="3"/>
+      <c r="N1002" s="1"/>
+      <c r="O1002" s="1"/>
+      <c r="P1002" s="1"/>
+      <c r="Q1002" s="1"/>
+      <c r="R1002" s="1"/>
+      <c r="S1002" s="1"/>
+      <c r="T1002" s="1"/>
+      <c r="U1002" s="1"/>
+      <c r="V1002" s="1"/>
+      <c r="W1002" s="1"/>
+      <c r="X1002" s="1"/>
+      <c r="Y1002" s="1"/>
+      <c r="Z1002" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C58:C1001 C1:C46" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C59:C1002 C1:C12 C14:C47" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"nominal,ordinal,interval,ratio,dateTime"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E1:E1001" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E14:E1002 E1:E12" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"text,enumerated,dateTime,numeric"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F1:F1001" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F14:F1002 F1:F12" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"ratio,interval"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H1:H1001" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H14:H1002 H1:H12" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"natural,whole,integer,real"</formula1>
     </dataValidation>
   </dataValidations>
